--- a/output/graficos_dimensiones/comunal_d_env_a_2020_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2020_valparaiso.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 22:16</t>
+    <t xml:space="preserve">2026-09-10 01:30</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2020_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2020_valparaiso.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:30</t>
+    <t xml:space="preserve">2026-09-12 22:41</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2020_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2020_valparaiso.xlsx
@@ -69,15 +69,15 @@
     <t xml:space="preserve">Nogales</t>
   </si>
   <si>
+    <t xml:space="preserve">Santo Domingo</t>
+  </si>
+  <si>
     <t xml:space="preserve">Limache</t>
   </si>
   <si>
     <t xml:space="preserve">Quillota</t>
   </si>
   <si>
-    <t xml:space="preserve">Santo Domingo</t>
-  </si>
-  <si>
     <t xml:space="preserve">Putaendo</t>
   </si>
   <si>
@@ -93,27 +93,27 @@
     <t xml:space="preserve">San Antonio</t>
   </si>
   <si>
+    <t xml:space="preserve">Panquehue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los Andes</t>
+  </si>
+  <si>
     <t xml:space="preserve">Calera</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Andes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Panquehue</t>
-  </si>
-  <si>
     <t xml:space="preserve">Catemu</t>
   </si>
   <si>
+    <t xml:space="preserve">Cabildo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hijuelas</t>
+  </si>
+  <si>
     <t xml:space="preserve">Puchuncaví</t>
   </si>
   <si>
-    <t xml:space="preserve">Hijuelas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cabildo</t>
-  </si>
-  <si>
     <t xml:space="preserve">Casablanca</t>
   </si>
   <si>
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 22:41</t>
+    <t xml:space="preserve">2026-09-24 00:10</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -589,7 +589,7 @@
         <v>2020</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>165.64</v>
+        <v>176.75</v>
       </c>
     </row>
     <row r="3">
@@ -606,7 +606,7 @@
         <v>2020</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>159.92</v>
+        <v>170.06</v>
       </c>
     </row>
     <row r="4">
@@ -623,7 +623,7 @@
         <v>2020</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>152.86</v>
+        <v>164.17</v>
       </c>
     </row>
     <row r="5">
@@ -640,7 +640,7 @@
         <v>2020</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>139.6</v>
+        <v>150.3</v>
       </c>
     </row>
     <row r="6">
@@ -657,7 +657,7 @@
         <v>2020</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>134.1</v>
+        <v>144.62</v>
       </c>
     </row>
     <row r="7">
@@ -674,7 +674,7 @@
         <v>2020</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>130.44</v>
+        <v>140.35</v>
       </c>
     </row>
     <row r="8">
@@ -691,7 +691,7 @@
         <v>2020</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>127.36</v>
+        <v>136.91</v>
       </c>
     </row>
     <row r="9">
@@ -708,7 +708,7 @@
         <v>2020</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>124.78</v>
+        <v>133</v>
       </c>
     </row>
     <row r="10">
@@ -725,7 +725,7 @@
         <v>2020</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>121.71</v>
+        <v>131.12</v>
       </c>
     </row>
     <row r="11">
@@ -742,7 +742,7 @@
         <v>2020</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>120.59</v>
+        <v>129.64</v>
       </c>
     </row>
     <row r="12">
@@ -759,7 +759,7 @@
         <v>2020</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>119.12</v>
+        <v>128.62</v>
       </c>
     </row>
     <row r="13">
@@ -776,7 +776,7 @@
         <v>2020</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>118.05</v>
+        <v>127.37</v>
       </c>
     </row>
     <row r="14">
@@ -787,13 +787,13 @@
         <v>17</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>5802</v>
+        <v>5606</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>2020</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>116.18</v>
+        <v>126.01</v>
       </c>
     </row>
     <row r="15">
@@ -804,13 +804,13 @@
         <v>18</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>5501</v>
+        <v>5802</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>2020</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>115.62</v>
+        <v>124.88</v>
       </c>
     </row>
     <row r="16">
@@ -821,13 +821,13 @@
         <v>19</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>5606</v>
+        <v>5501</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>2020</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>115.23</v>
+        <v>124.46</v>
       </c>
     </row>
     <row r="17">
@@ -844,7 +844,7 @@
         <v>2020</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>112.65</v>
+        <v>121.44</v>
       </c>
     </row>
     <row r="18">
@@ -861,7 +861,7 @@
         <v>2020</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>111.43</v>
+        <v>119.73</v>
       </c>
     </row>
     <row r="19">
@@ -878,7 +878,7 @@
         <v>2020</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>111.36</v>
+        <v>119.59</v>
       </c>
     </row>
     <row r="20">
@@ -895,7 +895,7 @@
         <v>2020</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>109.67</v>
+        <v>118.07</v>
       </c>
     </row>
     <row r="21">
@@ -912,7 +912,7 @@
         <v>2020</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>109.37</v>
+        <v>117.47</v>
       </c>
     </row>
     <row r="22">
@@ -923,13 +923,13 @@
         <v>25</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>5502</v>
+        <v>5704</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>2020</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>106.34</v>
+        <v>114.33</v>
       </c>
     </row>
     <row r="23">
@@ -946,7 +946,7 @@
         <v>2020</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>105.88</v>
+        <v>114.11</v>
       </c>
     </row>
     <row r="24">
@@ -957,13 +957,13 @@
         <v>27</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>5704</v>
+        <v>5502</v>
       </c>
       <c r="D24" s="2" t="n">
         <v>2020</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>104.58</v>
+        <v>113.94</v>
       </c>
     </row>
     <row r="25">
@@ -980,7 +980,7 @@
         <v>2020</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>103.93</v>
+        <v>111.91</v>
       </c>
     </row>
     <row r="26">
@@ -991,13 +991,13 @@
         <v>29</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>5105</v>
+        <v>5402</v>
       </c>
       <c r="D26" s="2" t="n">
         <v>2020</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>101.89</v>
+        <v>109.64</v>
       </c>
     </row>
     <row r="27">
@@ -1014,7 +1014,7 @@
         <v>2020</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>101.69</v>
+        <v>108.86</v>
       </c>
     </row>
     <row r="28">
@@ -1025,13 +1025,13 @@
         <v>31</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>5402</v>
+        <v>5105</v>
       </c>
       <c r="D28" s="2" t="n">
         <v>2020</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>101.54</v>
+        <v>108.78</v>
       </c>
     </row>
     <row r="29">
@@ -1048,7 +1048,7 @@
         <v>2020</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>98.83</v>
+        <v>105.91</v>
       </c>
     </row>
     <row r="30">
@@ -1065,7 +1065,7 @@
         <v>2020</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>98.81</v>
+        <v>105.39</v>
       </c>
     </row>
     <row r="31">
@@ -1082,7 +1082,7 @@
         <v>2020</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>96.61</v>
+        <v>103.14</v>
       </c>
     </row>
     <row r="32">
@@ -1099,7 +1099,7 @@
         <v>2020</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>93.76</v>
+        <v>100.4</v>
       </c>
     </row>
     <row r="33">
@@ -1116,7 +1116,7 @@
         <v>2020</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>93.15</v>
+        <v>100.11</v>
       </c>
     </row>
     <row r="34">
@@ -1133,7 +1133,7 @@
         <v>2020</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>92.9</v>
+        <v>99.51</v>
       </c>
     </row>
     <row r="35">
@@ -1150,7 +1150,7 @@
         <v>2020</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>87</v>
+        <v>93.94</v>
       </c>
     </row>
     <row r="36">
@@ -1167,7 +1167,7 @@
         <v>2020</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>85.87</v>
+        <v>91.5</v>
       </c>
     </row>
     <row r="37">
@@ -1184,7 +1184,7 @@
         <v>2020</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>75.56</v>
+        <v>80.98</v>
       </c>
     </row>
     <row r="38">
@@ -1201,7 +1201,7 @@
         <v>2020</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>74.37</v>
+        <v>80.43</v>
       </c>
     </row>
     <row r="39">
@@ -1218,7 +1218,7 @@
         <v>2020</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>45.62</v>
+        <v>48.36</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_d_env_a_2020_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2020_valparaiso.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:10</t>
+    <t xml:space="preserve">2026-10-02 16:09</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2020_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2020_valparaiso.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 16:09</t>
+    <t xml:space="preserve">2026-10-04 10:41</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2020_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2020_valparaiso.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 10:41</t>
+    <t xml:space="preserve">2026-10-05 16:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
